--- a/Result/profitability/6261.xlsx
+++ b/Result/profitability/6261.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.19</v>
       </c>
       <c r="M2" t="n">
-        <v>1.00125</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>30.95625</v>
+        <v>30.9275</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>1.21</v>
+        <v>1.25375</v>
       </c>
       <c r="N3" t="n">
-        <v>32.9925</v>
+        <v>33.46125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.04</v>
       </c>
       <c r="M4" t="n">
-        <v>1.34</v>
+        <v>1.3925</v>
       </c>
       <c r="N4" t="n">
-        <v>35.10125</v>
+        <v>35.59625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>1.32125</v>
+        <v>1.44125</v>
       </c>
       <c r="N5" t="n">
-        <v>35.63875</v>
+        <v>35.50125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.325</v>
+        <v>1.32</v>
       </c>
       <c r="N6" t="n">
-        <v>33.59</v>
+        <v>33.09625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.27625</v>
+        <v>1.2525</v>
       </c>
       <c r="N7" t="n">
-        <v>33.83625</v>
+        <v>33.665</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2625</v>
+        <v>1.325</v>
       </c>
       <c r="N8" t="n">
-        <v>35.645</v>
+        <v>35.4025</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>1.4375</v>
       </c>
       <c r="N12" t="n">
-        <v>36.45999999999999</v>
+        <v>36.46</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6261</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1074</v>
+      </c>
+      <c r="D75" t="n">
+        <v>760</v>
+      </c>
+      <c r="E75" t="n">
+        <v>314</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>116</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>151</v>
+      </c>
+      <c r="K75" t="n">
+        <v>174</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.02125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5882352941176472</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.940000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0622393326916908</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.099999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03626772172766235</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
